--- a/public/templates/visitor_import_template.xlsx
+++ b/public/templates/visitor_import_template.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="33">
   <si>
     <t>visitor_name</t>
   </si>
@@ -56,7 +56,7 @@
     <t>Meeting</t>
   </si>
   <si>
-    <t>P001</t>
+    <t>P0-01</t>
   </si>
   <si>
     <t>01/05/2026 09:00</t>
@@ -80,7 +80,7 @@
     <t>Interview</t>
   </si>
   <si>
-    <t>P002</t>
+    <t>P0-02</t>
   </si>
   <si>
     <t>02/05/2026 10:30</t>
@@ -90,6 +90,30 @@
   </si>
   <si>
     <t>HR interview round 2</t>
+  </si>
+  <si>
+    <t>Kevin Tan</t>
+  </si>
+  <si>
+    <t>Delta Logistics</t>
+  </si>
+  <si>
+    <t>Farah</t>
+  </si>
+  <si>
+    <t>Delivery</t>
+  </si>
+  <si>
+    <t>P0-03</t>
+  </si>
+  <si>
+    <t>03/05/2026 14:00</t>
+  </si>
+  <si>
+    <t>03/05/2026 15:30</t>
+  </si>
+  <si>
+    <t>Office furniture</t>
   </si>
 </sst>
 </file>
@@ -439,7 +463,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="15.282" bestFit="true" customWidth="true" style="0"/>
@@ -540,6 +564,35 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4">
+        <v>790404123456</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
